--- a/employee_reports/ubaid_khan.xlsx
+++ b/employee_reports/ubaid_khan.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Attendance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attendance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -470,25 +470,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Late</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ubaid khan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>19:25</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>19:26</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Late</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>610</v>
       </c>
     </row>
